--- a/test1.xlsx
+++ b/test1.xlsx
@@ -424,11 +424,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="29"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
+    <col customWidth="1" max="2" min="2" width="25"/>
     <col customWidth="1" max="3" min="3" width="23"/>
-    <col customWidth="1" max="4" min="4" width="19"/>
+    <col customWidth="1" max="4" min="4" width="22"/>
     <col customWidth="1" max="5" min="5" width="23"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col customWidth="1" max="6" min="6" width="19"/>
     <col customWidth="1" max="7" min="7" width="23"/>
     <col customWidth="1" max="8" min="8" width="22"/>
     <col customWidth="1" max="9" min="9" width="22"/>
@@ -445,7 +445,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>疫情好恐怖</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>可樂旅遊</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>0935888727</t>
+          <t>25112556</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>22-04-001</t>
+          <t>22-04-002</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>測試人員2</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>4/1 13:00</t>
+          <t>5/1 16:00</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>4/2 13:00</t>
+          <t>5/1 20:00</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>台北101</t>
         </is>
       </c>
       <c r="I2" s="1" t="n"/>
@@ -602,11 +602,7 @@
           <t>800</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
@@ -617,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>1</v>
@@ -631,11 +627,11 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -645,14 +641,10 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
@@ -663,25 +655,21 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -691,14 +679,10 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
@@ -709,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>2</v>
@@ -723,30 +707,38 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="n"/>
@@ -1119,7 +1111,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>廢版</t>
+          <t>紙箱</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1132,21 +1124,13 @@
           <t>寬度</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
+      <c r="E20" s="1" t="inlineStr"/>
       <c r="F20" s="1" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr">
         <is>
           <t>隻</t>
@@ -1184,7 +1168,7 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1194,7 +1178,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
@@ -1224,21 +1208,13 @@
           <t>高度</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="E22" s="1" t="inlineStr"/>
       <c r="F22" s="1" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
           <t>隻</t>
@@ -1268,13 +1244,13 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>X展架</t>
+          <t>易拉展</t>
         </is>
       </c>
       <c r="F23" s="1" t="n"/>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
@@ -1301,7 +1277,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1312,7 +1288,7 @@
       <c r="F24" s="1" t="n"/>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
